--- a/templates/513958_郑州移动PK赛日通报_模版.xlsx
+++ b/templates/513958_郑州移动PK赛日通报_模版.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuyu\Desktop\项目\自动通报\runtime\template_updater\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D761CD-A862-45CE-A3CE-9E561F59ADFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6D5E7B-ACFB-44E7-9BA2-068D10E4946D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{47518A48-49E1-4CBC-BF1D-7AFAA356E3CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{47518A48-49E1-4CBC-BF1D-7AFAA356E3CB}"/>
   </bookViews>
   <sheets>
     <sheet name="日通报" sheetId="1" r:id="rId1"/>
